--- a/tour-finance/output/metrics_all.xlsx
+++ b/tour-finance/output/metrics_all.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17.226</t>
+          <t>103.5567</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>11.255</t>
+          <t>63.7345</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>90.3468</t>
+          <t>37.8673</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -726,7 +726,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13.1074</t>
+          <t>86.5767</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.1676</t>
+          <t>57.4638</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>104.9533</t>
+          <t>56.6571</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -834,7 +834,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18.5136</t>
+          <t>92.3838</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>10.6051</t>
+          <t>60.02</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>121.8953</t>
+          <t>72.4804</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.1313</t>
+          <t>82.438</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.3592</t>
+          <t>50.121</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>116.8573</t>
+          <t>76.0955</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16.5148</t>
+          <t>82.7726</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>8.5246</t>
+          <t>45.9555</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>84.9768</t>
+          <t>47.5459</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21.6809</t>
+          <t>100.259</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.6938</t>
+          <t>46.4519</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>71.5805</t>
+          <t>34.8223</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24.0261</t>
+          <t>109.0545</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>10.4548</t>
+          <t>47.8776</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>18.9172</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>24.9257</t>
+          <t>116.1073</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>10.941</t>
+          <t>50.3249</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>49.5479</t>
+          <t>10.164</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>27.178</t>
+          <t>125.4391</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>10.6664</t>
+          <t>49.4483</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>49.1502</t>
+          <t>10.3683</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.9274</t>
+          <t>118.8396</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>10.7569</t>
+          <t>50.4302</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>52.4888</t>
+          <t>12.8155</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27.8009</t>
+          <t>118.1475</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>10.8526</t>
+          <t>48.777</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>50.1435</t>
+          <t>12.2191</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>27.1355</t>
+          <t>118.7525</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>11.8743</t>
+          <t>51.2052</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>49.5423</t>
+          <t>10.2114</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>29.7245</t>
+          <t>123.5575</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>11.6141</t>
+          <t>49.4938</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>41.324</t>
+          <t>3.4443</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>28.1357</t>
+          <t>123.9741</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2038,12 +2038,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>11.844</t>
+          <t>50.67</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>41.7304</t>
+          <t>2.9044</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>34.2695</t>
+          <t>122.2089</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>11.8794</t>
+          <t>46.8634</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>36.1948</t>
+          <t>1.2108</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>33.1553</t>
+          <t>140.7969</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>13.0858</t>
+          <t>51.0442</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>31.8043</t>
+          <t>-6.154</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>122.0333</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>12.5444</t>
+          <t>50.7199</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>27.6284</t>
+          <t>-10.547</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28.0287</t>
+          <t>118.6004</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>11.6437</t>
+          <t>46.7922</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>30.5733</t>
+          <t>-4.5753</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>27.6193</t>
+          <t>119.9902</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>10.8187</t>
+          <t>46.3853</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>31.439</t>
+          <t>-4.1276</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>32.8516</t>
+          <t>150.3216</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>11.6477</t>
+          <t>52.0667</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>27.1333</t>
+          <t>-13.2856</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -11268,7 +11268,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>12560.738</t>
+          <t>14721.379</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>88.3603</t>
+          <t>104.0029</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>-32.0722</t>
+          <t>-16.4296</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>12245.698</t>
+          <t>14396.577</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>71.2537</t>
+          <t>83.638</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>-39.4862</t>
+          <t>-27.1019</t>
         </is>
       </c>
       <c r="T103" t="inlineStr"/>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>14057.042</t>
+          <t>16127.792</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>58.1994</t>
+          <t>67.5404</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>-43.0169</t>
+          <t>-33.6759</t>
         </is>
       </c>
       <c r="T104" t="inlineStr"/>
@@ -11596,7 +11596,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>14637.9953</t>
+          <t>16864.8165</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>49.0193</t>
+          <t>56.3608</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>-59.4125</t>
+          <t>-52.071</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>18889.532</t>
+          <t>20758.575</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>72.9838</t>
+          <t>81.8998</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>-30.0101</t>
+          <t>-21.0941</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>17198.61</t>
+          <t>19195.547</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>50.7602</t>
+          <t>56.198</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>-35.2856</t>
+          <t>-29.8479</t>
         </is>
       </c>
       <c r="T107" t="inlineStr"/>
@@ -11912,7 +11912,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>18590.806</t>
+          <t>20887.878</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>46.8316</t>
+          <t>52.4504</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>-38.123</t>
+          <t>-32.5041</t>
         </is>
       </c>
       <c r="T108" t="inlineStr"/>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>17052.2687</t>
+          <t>19372.9974</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>45.5044</t>
+          <t>51.3997</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>-45.3917</t>
+          <t>-39.4963</t>
         </is>
       </c>
       <c r="T109" t="inlineStr"/>
@@ -12120,7 +12120,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>17614.873</t>
+          <t>20232.1</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>48.4038</t>
+          <t>55.2984</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>-44.3549</t>
+          <t>-37.4603</t>
         </is>
       </c>
       <c r="T110" t="inlineStr"/>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>19429.147</t>
+          <t>21612.902</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>41.5268</t>
+          <t>46.9087</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>-46.2404</t>
+          <t>-40.8585</t>
         </is>
       </c>
       <c r="T111" t="inlineStr"/>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>19843.861</t>
+          <t>22006.368</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>45.3444</t>
+          <t>50.3626</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>-47.723</t>
+          <t>-42.7048</t>
         </is>
       </c>
       <c r="T112" t="inlineStr"/>
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>18487.3486</t>
+          <t>20564.3268</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>43.6545</t>
+          <t>48.4827</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>-43.4101</t>
+          <t>-38.5819</t>
         </is>
       </c>
       <c r="T113" t="inlineStr"/>
